--- a/templates/ka_promo_and_expense_template.xlsx
+++ b/templates/ka_promo_and_expense_template.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minghuipei/Documents/finance-data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A494A499-AA9F-E744-812E-DCA23D9EAB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E034FC-AFF4-2B48-81A6-FB91065FF782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29440" yWindow="1760" windowWidth="23080" windowHeight="15020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="112">
   <si>
     <t>KA promo and Expense计提程序</t>
   </si>
@@ -100,213 +100,210 @@
     <t>21910916</t>
   </si>
   <si>
+    <t>200307</t>
+  </si>
+  <si>
+    <t>需求2的Customer number</t>
+  </si>
+  <si>
+    <t>需求2的Brand</t>
+  </si>
+  <si>
+    <t>需求2计算出的数</t>
+  </si>
+  <si>
+    <t>ACE 当年当月 1% Marketing Allowance Accrual</t>
+  </si>
+  <si>
+    <t>需求2的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>200216</t>
+  </si>
+  <si>
+    <t>需求3的Customer number</t>
+  </si>
+  <si>
+    <t>需求3的Brand</t>
+  </si>
+  <si>
+    <t>需求3计算出的数</t>
+  </si>
+  <si>
+    <t>G10 当年当月 Promo Accrual</t>
+  </si>
+  <si>
+    <t>需求3的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求4的Customer number</t>
+  </si>
+  <si>
+    <t>需求4的Brand</t>
+  </si>
+  <si>
+    <t>需求4计算出的数</t>
+  </si>
+  <si>
+    <t>Amazon 当年当月 promo accrual</t>
+  </si>
+  <si>
+    <t>需求4的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求5计算出的数</t>
+  </si>
+  <si>
+    <t>需求5的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求6的Customer number</t>
+  </si>
+  <si>
+    <t>需求6的Brand</t>
+  </si>
+  <si>
+    <t>需求6计算出的数</t>
+  </si>
+  <si>
+    <t>需求6的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求7的Customer number</t>
+  </si>
+  <si>
+    <t>需求7的Brand</t>
+  </si>
+  <si>
+    <t>需求7计算出的数</t>
+  </si>
+  <si>
+    <t>需求7的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求8的Customer number</t>
+  </si>
+  <si>
+    <t>需求8的Brand</t>
+  </si>
+  <si>
+    <t>需求8计算出的数</t>
+  </si>
+  <si>
+    <t>需求8的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>需求5的Customer number</t>
+  </si>
+  <si>
+    <t>需求5的Brand</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>需求9的Customer number</t>
+  </si>
+  <si>
+    <t>需求9的Brand</t>
+  </si>
+  <si>
+    <t>需求9计算出的数</t>
+  </si>
+  <si>
+    <t>Lowes 当年当月 Co-op Marketing Accrual</t>
+  </si>
+  <si>
+    <t>需求9的Due Amount的合计</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>200212</t>
+  </si>
+  <si>
+    <t>900082</t>
+  </si>
+  <si>
+    <t>需求10的Customer number</t>
+  </si>
+  <si>
+    <t>需求10的Brand</t>
+  </si>
+  <si>
+    <t>需求10的计算出的数</t>
+  </si>
+  <si>
+    <t>Lowes 当年当月 Promo Accrual</t>
+  </si>
+  <si>
+    <t>需求10的计算出due amount合计</t>
+  </si>
+  <si>
+    <t>需求11的计算出的数</t>
+  </si>
+  <si>
+    <t>需求11的计算出due amount合计</t>
+  </si>
+  <si>
+    <t>需求12的Customer number</t>
+  </si>
+  <si>
+    <t>需求12的Brand</t>
+  </si>
+  <si>
+    <t>需求12的计算出的数</t>
+  </si>
+  <si>
+    <t>需求12的计算出due amount合计</t>
+  </si>
+  <si>
+    <t>需求13的Customer number</t>
+  </si>
+  <si>
+    <t>需求13的Brand</t>
+  </si>
+  <si>
+    <t>需求13的计算出的数</t>
+  </si>
+  <si>
+    <t>需求13的计算出due amount合计</t>
+  </si>
+  <si>
+    <t>需求14的Customer number</t>
+  </si>
+  <si>
+    <t>需求14的Brand</t>
+  </si>
+  <si>
+    <t>需求14的计算出的数</t>
+  </si>
+  <si>
+    <t>需求14的计算出due amount合计</t>
+  </si>
+  <si>
+    <t>需求15的Customer number</t>
+  </si>
+  <si>
+    <t>需求15的Brand</t>
+  </si>
+  <si>
+    <t>需求15的计算出的数</t>
+  </si>
+  <si>
+    <t>需求15的计算出due amount合计</t>
+  </si>
+  <si>
     <t>900209</t>
   </si>
   <si>
-    <t>需求2计算出的数</t>
-  </si>
-  <si>
-    <t>ACE 当年当月 1% Marketing Allowance Accrual</t>
-  </si>
-  <si>
-    <t>需求2的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求2的Customer number</t>
-  </si>
-  <si>
-    <t>需求2的Brand</t>
-  </si>
-  <si>
-    <t>200216</t>
-  </si>
-  <si>
-    <t>需求3的Customer number</t>
-  </si>
-  <si>
-    <t>需求3的Brand</t>
-  </si>
-  <si>
-    <t>需求3计算出的数</t>
-  </si>
-  <si>
-    <t>G10 当年当月 Promo Accrual</t>
-  </si>
-  <si>
-    <t>需求3的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求4的Customer number</t>
-  </si>
-  <si>
-    <t>需求4的Brand</t>
-  </si>
-  <si>
-    <t>需求4计算出的数</t>
-  </si>
-  <si>
-    <t>Amazon 当年当月 promo accrual</t>
-  </si>
-  <si>
-    <t>需求4的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求5的Customer number</t>
-  </si>
-  <si>
-    <t>需求5的Brand</t>
-  </si>
-  <si>
-    <t>需求5计算出的数</t>
-  </si>
-  <si>
-    <t>需求5的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求6的Customer number</t>
-  </si>
-  <si>
-    <t>需求6的Brand</t>
-  </si>
-  <si>
-    <t>需求6计算出的数</t>
-  </si>
-  <si>
-    <t>需求6的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求7的Customer number</t>
-  </si>
-  <si>
-    <t>需求7的Brand</t>
-  </si>
-  <si>
-    <t>需求7计算出的数</t>
-  </si>
-  <si>
-    <t>需求7的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>需求8的Customer number</t>
-  </si>
-  <si>
-    <t>需求8的Brand</t>
-  </si>
-  <si>
-    <t>需求8计算出的数</t>
-  </si>
-  <si>
-    <t>需求8的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>CR</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>需求9的Customer number</t>
-  </si>
-  <si>
-    <t>需求9的Brand</t>
-  </si>
-  <si>
-    <t>需求9计算出的数</t>
-  </si>
-  <si>
-    <t>Lowes 当年当月 Co-op Marketing Accrual</t>
-  </si>
-  <si>
-    <t>需求9的Due Amount的合计</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>200212</t>
-  </si>
-  <si>
-    <t>900082</t>
-  </si>
-  <si>
-    <t>需求10的Customer number</t>
-  </si>
-  <si>
-    <t>需求10的Brand</t>
-  </si>
-  <si>
-    <t>需求10的计算出的数</t>
-  </si>
-  <si>
-    <t>Lowes 当年当月 Promo Accrual</t>
-  </si>
-  <si>
-    <t>需求10的计算出due amount合计</t>
-  </si>
-  <si>
-    <t>需求11的Customer number</t>
-  </si>
-  <si>
-    <t>需求11的Brand</t>
-  </si>
-  <si>
-    <t>需求11的计算出的数</t>
-  </si>
-  <si>
-    <t>需求11的计算出due amount合计</t>
-  </si>
-  <si>
-    <t>需求12的Customer number</t>
-  </si>
-  <si>
-    <t>需求12的Brand</t>
-  </si>
-  <si>
-    <t>需求12的计算出的数</t>
-  </si>
-  <si>
-    <t>需求12的计算出due amount合计</t>
-  </si>
-  <si>
-    <t>需求13的Customer number</t>
-  </si>
-  <si>
-    <t>需求13的Brand</t>
-  </si>
-  <si>
-    <t>需求13的计算出的数</t>
-  </si>
-  <si>
-    <t>需求13的计算出due amount合计</t>
-  </si>
-  <si>
-    <t>需求14的Customer number</t>
-  </si>
-  <si>
-    <t>需求14的Brand</t>
-  </si>
-  <si>
-    <t>需求14的计算出的数</t>
-  </si>
-  <si>
-    <t>需求14的计算出due amount合计</t>
-  </si>
-  <si>
-    <t>需求15的Customer number</t>
-  </si>
-  <si>
-    <t>需求15的Brand</t>
-  </si>
-  <si>
-    <t>需求15的计算出的数</t>
-  </si>
-  <si>
-    <t>需求15的计算出due amount合计</t>
-  </si>
-  <si>
     <t>21330102</t>
   </si>
   <si>
@@ -316,49 +313,52 @@
     <t>需求10-15计算出的due amount的合计</t>
   </si>
   <si>
-    <t>99999999</t>
-  </si>
-  <si>
-    <t>需求16计算出的数合计</t>
+    <t>21910932</t>
+  </si>
+  <si>
+    <t>900085</t>
+  </si>
+  <si>
+    <t>0178</t>
+  </si>
+  <si>
+    <t>000030</t>
+  </si>
+  <si>
+    <t>需求16的计算出的对应brand数</t>
   </si>
   <si>
     <t>Lowes 当年当月 MST Accrual</t>
   </si>
   <si>
-    <t>需求16的计算出的所有Brand的Due amount合计</t>
-  </si>
-  <si>
-    <t>21910932</t>
-  </si>
-  <si>
-    <t>900085</t>
-  </si>
-  <si>
-    <t>0178</t>
-  </si>
-  <si>
-    <t>000030</t>
-  </si>
-  <si>
-    <t>需求16的计算出的对应brand数</t>
-  </si>
-  <si>
     <t>需求16的计算出的对应Brand的Due amount合计</t>
   </si>
   <si>
+    <t>000051</t>
+  </si>
+  <si>
+    <t>000070</t>
+  </si>
+  <si>
+    <t>000080</t>
+  </si>
+  <si>
+    <t>ODM002</t>
+  </si>
+  <si>
     <t>000050</t>
-  </si>
-  <si>
-    <t>000051</t>
-  </si>
-  <si>
-    <t>000070</t>
-  </si>
-  <si>
-    <t>000080</t>
-  </si>
-  <si>
-    <t>ODM002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200305</t>
+  </si>
+  <si>
+    <t>200305</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>55010428</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -492,7 +492,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -507,9 +507,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -536,6 +533,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -825,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -838,7 +840,7 @@
     <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" customWidth="1"/>
     <col min="10" max="10" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.1640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.1640625" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -878,23 +880,23 @@
       <c r="J3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
@@ -904,8 +906,8 @@
       <c r="J4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="12"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="11"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="3">
@@ -929,17 +931,17 @@
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="7"/>
+      <c r="J5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <v>0.11</v>
       </c>
     </row>
@@ -965,17 +967,17 @@
       <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>0.11</v>
       </c>
     </row>
@@ -1010,23 +1012,23 @@
       <c r="J9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1036,8 +1038,8 @@
       <c r="J10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="12"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="11"/>
     </row>
     <row r="11" spans="1:13" ht="14.5" customHeight="1">
       <c r="A11" s="3">
@@ -1047,31 +1049,31 @@
         <v>26</v>
       </c>
       <c r="C11" s="4">
-        <v>21330102</v>
+        <v>55010404</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="14" t="s">
+      <c r="H11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="M11" s="10">
+      <c r="I11" s="7"/>
+      <c r="J11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="9">
         <v>0.01</v>
       </c>
     </row>
@@ -1080,150 +1082,138 @@
         <v>203</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4">
-        <v>99999999</v>
+        <v>21910906</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="14.5" customHeight="1"/>
+    <row r="14" spans="1:13" ht="14.5" customHeight="1"/>
+    <row r="15" spans="1:13">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="15"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="3">
+        <v>203</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M12" s="10">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A13" s="3">
-        <v>203</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="4">
-        <v>99999999</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M13" s="10">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="14.5" customHeight="1">
-      <c r="A14" s="3">
-        <v>203</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="4">
-        <v>21910906</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="10">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>12</v>
+      <c r="E17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="9">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="19" t="s">
-        <v>13</v>
+      <c r="A18" s="19">
+        <v>203</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1231,131 +1221,119 @@
       <c r="E18" s="20"/>
       <c r="F18" s="20"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="6"/>
+      <c r="I18" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="3">
-        <v>203</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="L22" s="15"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="3">
+        <v>203</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="10">
+      <c r="E23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M23" s="9">
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="3">
-        <v>203</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="M20" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="19" t="s">
-        <v>13</v>
+      <c r="A24" s="19">
+        <v>203</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -1363,17 +1341,19 @@
       <c r="E24" s="20"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
-      <c r="H24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="12"/>
+      <c r="H24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" s="12">
+        <v>0.14499999999999999</v>
+      </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="3">
@@ -1389,26 +1369,26 @@
         <v>18</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="8"/>
+      <c r="H25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="7"/>
       <c r="J25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L25" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="M25" s="10">
-        <v>0.14000000000000001</v>
+      <c r="L25" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="12">
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -1425,26 +1405,26 @@
         <v>18</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="8"/>
+      <c r="H26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="7"/>
       <c r="J26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0.14499999999999999</v>
+      <c r="L26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -1461,26 +1441,26 @@
         <v>18</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="8"/>
+      <c r="H27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="7"/>
       <c r="J27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L27" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M27" s="13">
-        <v>0.14499999999999999</v>
+      <c r="L27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -1491,32 +1471,32 @@
         <v>32</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="8"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="J28" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L28" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M28" s="10">
-        <v>0.12</v>
+      <c r="L28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="9">
+        <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -1527,32 +1507,32 @@
         <v>32</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" s="8"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="J29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M29" s="10">
-        <v>0.12</v>
+      <c r="L29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="M29" s="12">
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -1569,26 +1549,26 @@
         <v>18</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7" t="s">
-        <v>40</v>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L30" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="M30" s="10">
-        <v>0.14000000000000001</v>
+      <c r="L30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M30" s="12">
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -1605,26 +1585,26 @@
         <v>18</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7" t="s">
-        <v>45</v>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="M31" s="13">
-        <v>0.14499999999999999</v>
+      <c r="L31" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M31" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -1641,141 +1621,127 @@
         <v>18</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7" t="s">
-        <v>49</v>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L32" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="13">
-        <v>0.14499999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
-      <c r="A33" s="3">
-        <v>203</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="L32" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L36" s="15"/>
+      <c r="M36" s="11"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="3">
+        <v>203</v>
+      </c>
+      <c r="B37" s="4">
+        <v>200305</v>
+      </c>
+      <c r="C37" s="4">
+        <v>55010425</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L33" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M33" s="10">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" s="3">
-        <v>203</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M34" s="10">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
-      <c r="A37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M37" s="11" t="s">
-        <v>12</v>
+      <c r="E37" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="J37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M37" s="12">
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="19" t="s">
-        <v>13</v>
+      <c r="A38" s="19">
+        <v>203</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="20"/>
@@ -1783,17 +1749,19 @@
       <c r="E38" s="20"/>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
-      <c r="H38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38" s="16"/>
-      <c r="M38" s="12"/>
+      <c r="H38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="J38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="M38" s="12">
+        <v>1.5E-3</v>
+      </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="3">
@@ -1817,17 +1785,17 @@
       <c r="G39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I39" s="8"/>
+      <c r="I39" s="7"/>
       <c r="J39" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L39" s="14" t="s">
+      <c r="L39" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M39" s="13">
+      <c r="M39" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1853,17 +1821,17 @@
       <c r="G40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I40" s="8"/>
+      <c r="I40" s="7"/>
       <c r="J40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L40" s="14" t="s">
+      <c r="L40" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M40" s="13">
+      <c r="M40" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1889,17 +1857,17 @@
       <c r="G41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I41" s="8"/>
+      <c r="I41" s="7"/>
       <c r="J41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L41" s="14" t="s">
+      <c r="L41" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M41" s="13">
+      <c r="M41" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1925,17 +1893,17 @@
       <c r="G42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I42" s="8"/>
+      <c r="I42" s="7"/>
       <c r="J42" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L42" s="14" t="s">
+      <c r="L42" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M42" s="13">
+      <c r="M42" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1947,7 +1915,7 @@
         <v>200305</v>
       </c>
       <c r="C43" s="4">
-        <v>55010425</v>
+        <v>21910906</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>18</v>
@@ -1961,17 +1929,17 @@
       <c r="G43" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I43" s="8"/>
       <c r="J43" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L43" s="14" t="s">
+      <c r="L43" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M43" s="13">
+      <c r="M43" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -1983,7 +1951,7 @@
         <v>200305</v>
       </c>
       <c r="C44" s="4">
-        <v>55010425</v>
+        <v>21910906</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>18</v>
@@ -1997,17 +1965,17 @@
       <c r="G44" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I44" s="8"/>
       <c r="J44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L44" s="14" t="s">
+      <c r="L44" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M44" s="13">
+      <c r="M44" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -2033,17 +2001,17 @@
       <c r="G45" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7" t="s">
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="s">
         <v>64</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L45" s="14" t="s">
+      <c r="L45" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M45" s="13">
+      <c r="M45" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -2069,17 +2037,17 @@
       <c r="G46" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7" t="s">
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L46" s="14" t="s">
+      <c r="L46" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M46" s="13">
+      <c r="M46" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -2105,17 +2073,17 @@
       <c r="G47" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7" t="s">
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="s">
         <v>64</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L47" s="14" t="s">
+      <c r="L47" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M47" s="13">
+      <c r="M47" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
@@ -2141,146 +2109,132 @@
       <c r="G48" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7" t="s">
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="s">
         <v>64</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="L48" s="14" t="s">
+      <c r="L48" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="M48" s="13">
+      <c r="M48" s="12">
         <v>1.5E-3</v>
       </c>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="3">
-        <v>203</v>
-      </c>
-      <c r="B49" s="4">
-        <v>200305</v>
-      </c>
-      <c r="C49" s="4">
-        <v>21910906</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L49" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M49" s="13">
-        <v>1.5E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="3">
-        <v>203</v>
-      </c>
-      <c r="B50" s="4">
-        <v>200305</v>
-      </c>
-      <c r="C50" s="4">
-        <v>21910906</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L50" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M50" s="13">
-        <v>1.5E-3</v>
-      </c>
+      <c r="A49" s="3"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="3"/>
+      <c r="M49" s="12"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="3"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="3"/>
-      <c r="M51" s="13"/>
+      <c r="A51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L52" s="15"/>
+      <c r="M52" s="11"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L53" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M53" s="11" t="s">
-        <v>12</v>
+      <c r="A53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I53" s="5"/>
+      <c r="J53" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M53" s="12">
+        <v>0.02</v>
       </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="19" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -2288,17 +2242,19 @@
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
-      <c r="H54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L54" s="16"/>
-      <c r="M54" s="12"/>
+      <c r="H54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I54" s="5"/>
+      <c r="J54" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M54" s="12">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="3" t="s">
@@ -2314,25 +2270,25 @@
         <v>69</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H55" s="7" t="s">
-        <v>72</v>
+      <c r="H55" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L55" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="M55" s="13">
+      <c r="L55" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M55" s="12">
         <v>0.02</v>
       </c>
     </row>
@@ -2350,25 +2306,25 @@
         <v>69</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H56" s="7" t="s">
-        <v>77</v>
+      <c r="H56" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="I56" s="5"/>
       <c r="J56" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L56" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="M56" s="13">
+      <c r="L56" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M56" s="12">
         <v>0.02</v>
       </c>
     </row>
@@ -2386,25 +2342,25 @@
         <v>69</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H57" s="7" t="s">
-        <v>81</v>
+      <c r="H57" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L57" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="M57" s="13">
+      <c r="L57" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M57" s="12">
         <v>0.02</v>
       </c>
     </row>
@@ -2422,301 +2378,305 @@
         <v>69</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H58" s="7" t="s">
-        <v>85</v>
+      <c r="H58" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L58" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="M58" s="13">
+      <c r="L58" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M58" s="12">
         <v>0.02</v>
       </c>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="3" t="s">
-        <v>67</v>
+      <c r="A59" s="3">
+        <v>203</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H59" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I59" s="5"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="J59" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="L59" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="M59" s="13">
-        <v>0.02</v>
-      </c>
+      <c r="L59" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="M59" s="12"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="I60" s="5"/>
-      <c r="J60" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L60" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="M60" s="13">
-        <v>0.02</v>
-      </c>
+      <c r="J60" s="3"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="3">
-        <v>203</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L61" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="M61" s="13"/>
+      <c r="J61" s="3"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="J62" s="3"/>
+      <c r="A62" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L62" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="J63" s="3"/>
+      <c r="A63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" s="15"/>
+      <c r="M63" s="11"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L64" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="M64" s="11" t="s">
-        <v>12</v>
+      <c r="A64" s="3">
+        <v>203</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I64" s="6"/>
+      <c r="J64" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L64" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M64" s="12">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" s="16"/>
-      <c r="M65" s="12"/>
+      <c r="A65" s="3">
+        <v>203</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C65" s="3">
+        <v>55010428</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I65" s="6"/>
+      <c r="J65" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L65" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M65" s="12">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="3">
         <v>203</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="E66" s="5" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>18</v>
+        <v>104</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="7"/>
-      <c r="I66" s="5" t="s">
-        <v>99</v>
-      </c>
+      <c r="H66" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I66" s="6"/>
       <c r="J66" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L66" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="M66" s="13"/>
+        <v>102</v>
+      </c>
+      <c r="L66" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M66" s="12">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="3">
         <v>203</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H67" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="I67" s="5"/>
+      <c r="H67" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I67" s="6"/>
       <c r="J67" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L67" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="M67" s="13"/>
+        <v>102</v>
+      </c>
+      <c r="L67" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M67" s="12">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="3">
         <v>203</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I68" s="6"/>
+      <c r="J68" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="L68" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L68" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M68" s="13">
+      <c r="M68" s="12">
         <v>0.1</v>
       </c>
     </row>
@@ -2725,35 +2685,35 @@
         <v>203</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I69" s="6"/>
+      <c r="J69" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="L69" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="7"/>
-      <c r="I69" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L69" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M69" s="13">
-        <v>0.08</v>
+      <c r="M69" s="12">
+        <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -2764,32 +2724,32 @@
         <v>68</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="L70" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L70" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M70" s="13">
-        <v>0.08</v>
+      <c r="M70" s="12">
+        <v>0.1</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -2800,31 +2760,31 @@
         <v>68</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J71" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="L71" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" s="7"/>
-      <c r="I71" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L71" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M71" s="13">
+      <c r="M71" s="12">
         <v>0.1</v>
       </c>
     </row>
@@ -2836,32 +2796,32 @@
         <v>68</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J72" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="L72" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L72" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M72" s="13">
-        <v>0.1</v>
+      <c r="M72" s="12">
+        <v>0.08</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -2872,32 +2832,32 @@
         <v>68</v>
       </c>
       <c r="C73" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J73" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="L73" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="7"/>
-      <c r="I73" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L73" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="M73" s="13">
-        <v>0.19500000000000001</v>
+      <c r="M73" s="12">
+        <v>0.1</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -2905,38 +2865,75 @@
         <v>203</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="E74" s="5" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="6"/>
+      <c r="I74" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L74" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M74" s="12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="3">
+        <v>203</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="I74" s="5"/>
-      <c r="J74" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L74" s="18" t="s">
+      <c r="F75" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="M74" s="13"/>
+      <c r="J75" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L75" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M75" s="12">
+        <v>0.19500000000000001</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A65:G65"/>
+  <mergeCells count="6">
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A4:G4"/>

--- a/templates/ka_promo_and_expense_template.xlsx
+++ b/templates/ka_promo_and_expense_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minghuipei/Documents/finance-data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E034FC-AFF4-2B48-81A6-FB91065FF782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCA3B66-0C57-084C-9845-D390684A62A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="116">
   <si>
     <t>KA promo and Expense计提程序</t>
   </si>
@@ -358,6 +358,22 @@
   </si>
   <si>
     <t>55010428</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求5的Customer number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求5的Brand</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求11的Customer number</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求11的Brand</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +508,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -534,10 +550,6 @@
     </xf>
     <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -888,15 +900,15 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
       <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1020,15 +1032,15 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
       <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1212,15 +1224,27 @@
       </c>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="19">
-        <v>203</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
+      <c r="A18" s="3">
+        <v>203</v>
+      </c>
+      <c r="B18" s="3">
+        <v>200216</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H18" s="6"/>
       <c r="I18" s="7" t="s">
         <v>35</v>
@@ -1332,15 +1356,27 @@
       </c>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="19">
-        <v>203</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
+      <c r="A24" s="3">
+        <v>203</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H24" s="6" t="s">
         <v>43</v>
       </c>
@@ -1740,15 +1776,27 @@
       </c>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="19">
-        <v>203</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+      <c r="A38" s="3">
+        <v>203</v>
+      </c>
+      <c r="B38" s="4">
+        <v>200305</v>
+      </c>
+      <c r="C38" s="4">
+        <v>55010425</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H38" s="6" t="s">
         <v>64</v>
       </c>
@@ -2233,15 +2281,27 @@
       </c>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+      <c r="B54" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H54" s="6" t="s">
         <v>75</v>
       </c>
@@ -2933,13 +2993,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="2">
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A54:G54"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
